--- a/data/sample_reports/corporate_filing.xlsx
+++ b/data/sample_reports/corporate_filing.xlsx
@@ -514,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -593,6 +593,24 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>150000000</v>
+      </c>
+      <c r="C5" t="n">
+        <v>180000000</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Healthy asset base driven by organic growth.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
